--- a/artfynd/A 27787-2026 artfynd.xlsx
+++ b/artfynd/A 27787-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102491888</v>
+        <v>134574738</v>
       </c>
       <c r="B2" t="n">
-        <v>89292</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slångsåsen, Sundsvall, Mpd</t>
+          <t>Norra bodmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583674</v>
+        <v>583649</v>
       </c>
       <c r="R2" t="n">
-        <v>6928720</v>
+        <v>6928771</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,45 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cecilia Öster, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102491893</v>
+        <v>134574740</v>
       </c>
       <c r="B3" t="n">
-        <v>92208</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slångsåsen, Sundsvall, Mpd</t>
+          <t>Norra bodmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583706</v>
+        <v>583683</v>
       </c>
       <c r="R3" t="n">
-        <v>6928890</v>
+        <v>6928782</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,45 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cecilia Öster, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90487530</v>
+        <v>134574742</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Härnosand_8178, Mpd</t>
+          <t>Norra bodmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583728</v>
+        <v>583693</v>
       </c>
       <c r="R4" t="n">
-        <v>6928792</v>
+        <v>6928830</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,12 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-30</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,26 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charles Campbell, Beren van Duijn, Olle Finnström, Maria Jakobsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Härnösand - Greensway AB</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102491894</v>
+        <v>134574746</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,37 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slångsåsen, Sundsvall, Mpd</t>
+          <t>Norra bodmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583705</v>
+        <v>583702</v>
       </c>
       <c r="R5" t="n">
-        <v>6928891</v>
+        <v>6928700</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,12 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,83 +1087,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cecilia Öster, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102491887</v>
+        <v>134574744</v>
       </c>
       <c r="B6" t="n">
-        <v>80432</v>
+        <v>80351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>392</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slångsåsen, Sundsvall, Mpd</t>
+          <t>Norra bodmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583667</v>
+        <v>583740</v>
       </c>
       <c r="R6" t="n">
-        <v>6928704</v>
+        <v>6928758</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,12 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,45 +1194,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Cecilia Öster, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102491889</v>
+        <v>102491888</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583685</v>
+        <v>583674</v>
       </c>
       <c r="R7" t="n">
-        <v>6928752</v>
+        <v>6928720</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,17 +1294,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1356,32 +1326,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102491886</v>
+        <v>102491893</v>
       </c>
       <c r="B8" t="n">
-        <v>80467</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583667</v>
+        <v>583706</v>
       </c>
       <c r="R8" t="n">
-        <v>6928703</v>
+        <v>6928890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,17 +1410,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1472,48 +1442,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102491890</v>
+        <v>90487530</v>
       </c>
       <c r="B9" t="n">
-        <v>80392</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Slångsåsen, Sundsvall, Mpd</t>
+          <t>Härnosand_8178, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583706</v>
+        <v>583728</v>
       </c>
       <c r="R9" t="n">
-        <v>6928788</v>
+        <v>6928792</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,12 +1507,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,38 +1523,1365 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Charles Campbell, Beren van Duijn, Olle Finnström, Maria Jakobsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Härnösand - Greensway AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>102491894</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Slångsåsen, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>583705</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6928891</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Carl Jansson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Carl Jansson, Cecilia Öster, Roger Adolfsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134574735</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norra bodmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>583699</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6928707</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134574737</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norra bodmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>583647</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6928779</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134574743</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norra bodmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>583705</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6928841</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>102491887</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Slångsåsen, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>583667</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6928704</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Cecilia Öster, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>102491889</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Slångsåsen, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>583685</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6928752</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Cecilia Öster, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134574736</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norra bodmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>583664</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6928740</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134574741</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norra bodmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>583678</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6928819</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>102491886</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Slångsåsen, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>583667</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6928703</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Cecilia Öster, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134574734</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norra bodmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>583674</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6928689</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>102491890</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Slångsåsen, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>583706</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6928788</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Cecilia Öster, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134574739</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norra bodmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>583678</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6928752</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27787-2026 artfynd.xlsx
+++ b/artfynd/A 27787-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574738</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574740</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574742</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574746</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574744</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102491888</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102491893</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
           <t>Härnösand - Greensway AB</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90487530</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102491894</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1763,6 +1813,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574735</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574737</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1977,6 +2037,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574743</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102491887</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2209,6 +2279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102491889</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2316,6 +2391,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574736</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2423,6 +2503,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574741</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2539,6 +2624,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102491886</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2659,6 +2749,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574734</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2775,6 +2870,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102491890</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2882,8 +2982,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134574739</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>